--- a/projects/cumcm2026b/artifacts/results/resultB.xlsx
+++ b/projects/cumcm2026b/artifacts/results/resultB.xlsx
@@ -783,16 +783,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>7874.49</v>
+        <v>6389.05</v>
       </c>
       <c r="F2" t="n">
-        <v>25347.47</v>
+        <v>22995.24</v>
       </c>
       <c r="G2" t="n">
-        <v>546</v>
+        <v>343</v>
       </c>
       <c r="H2" t="n">
-        <v>5523.64</v>
+        <v>4226.16</v>
       </c>
     </row>
     <row r="3">
@@ -809,16 +809,16 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>6779.69</v>
+        <v>5663.43</v>
       </c>
       <c r="F3" t="n">
-        <v>20073.47</v>
+        <v>19567.16</v>
       </c>
       <c r="G3" t="n">
-        <v>543</v>
+        <v>340</v>
       </c>
       <c r="H3" t="n">
-        <v>4828.94</v>
+        <v>4109.02</v>
       </c>
     </row>
     <row r="4">
@@ -835,16 +835,16 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>7023.37</v>
+        <v>6016.22</v>
       </c>
       <c r="F4" t="n">
-        <v>21291.83</v>
+        <v>21181.1</v>
       </c>
       <c r="G4" t="n">
-        <v>540</v>
+        <v>343</v>
       </c>
       <c r="H4" t="n">
-        <v>5093</v>
+        <v>4096.98</v>
       </c>
     </row>
     <row r="5">
@@ -861,16 +861,16 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>7035.31</v>
+        <v>5905.64</v>
       </c>
       <c r="F5" t="n">
-        <v>21301.53</v>
+        <v>20653.2</v>
       </c>
       <c r="G5" t="n">
-        <v>543</v>
+        <v>343</v>
       </c>
       <c r="H5" t="n">
-        <v>4937.89</v>
+        <v>3846.24</v>
       </c>
     </row>
     <row r="6">
@@ -887,16 +887,16 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>6793.72</v>
+        <v>5744.26</v>
       </c>
       <c r="F6" t="n">
-        <v>20218.59</v>
+        <v>19971.3</v>
       </c>
       <c r="G6" t="n">
-        <v>540</v>
+        <v>340</v>
       </c>
       <c r="H6" t="n">
-        <v>4917.74</v>
+        <v>4088.59</v>
       </c>
     </row>
     <row r="7">
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>6990.27</v>
+        <v>5804.17</v>
       </c>
       <c r="F7" t="n">
-        <v>21076.35</v>
+        <v>20145.85</v>
       </c>
       <c r="G7" t="n">
-        <v>543</v>
+        <v>343</v>
       </c>
       <c r="H7" t="n">
-        <v>4966.36</v>
+        <v>3683.71</v>
       </c>
     </row>
     <row r="8">
@@ -939,16 +939,16 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>7415.09</v>
+        <v>6519.21</v>
       </c>
       <c r="F8" t="n">
-        <v>23150.46</v>
+        <v>23671.04</v>
       </c>
       <c r="G8" t="n">
-        <v>543</v>
+        <v>343</v>
       </c>
       <c r="H8" t="n">
-        <v>5439.29</v>
+        <v>4607.3</v>
       </c>
     </row>
     <row r="9">
@@ -965,16 +965,16 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>6941.66</v>
+        <v>6088.65</v>
       </c>
       <c r="F9" t="n">
-        <v>20883.31</v>
+        <v>21693.27</v>
       </c>
       <c r="G9" t="n">
-        <v>543</v>
+        <v>340</v>
       </c>
       <c r="H9" t="n">
-        <v>5308.28</v>
+        <v>4073.18</v>
       </c>
     </row>
     <row r="10">
@@ -991,16 +991,16 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>7308.8</v>
+        <v>6469.35</v>
       </c>
       <c r="F10" t="n">
-        <v>22644.01</v>
+        <v>23371.77</v>
       </c>
       <c r="G10" t="n">
-        <v>543</v>
+        <v>346</v>
       </c>
       <c r="H10" t="n">
-        <v>5508.61</v>
+        <v>4257.39</v>
       </c>
     </row>
     <row r="11">
@@ -1017,16 +1017,16 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>7035.94</v>
+        <v>6157.96</v>
       </c>
       <c r="F11" t="n">
-        <v>21329.72</v>
+        <v>22014.78</v>
       </c>
       <c r="G11" t="n">
-        <v>543</v>
+        <v>340</v>
       </c>
       <c r="H11" t="n">
-        <v>4710.89</v>
+        <v>3851.62</v>
       </c>
     </row>
     <row r="12">
@@ -1043,16 +1043,16 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>6871.82</v>
+        <v>5853.01</v>
       </c>
       <c r="F12" t="n">
-        <v>20559.08</v>
+        <v>20390.03</v>
       </c>
       <c r="G12" t="n">
-        <v>540</v>
+        <v>343</v>
       </c>
       <c r="H12" t="n">
-        <v>5336.75</v>
+        <v>4223.82</v>
       </c>
     </row>
     <row r="13">
@@ -1069,16 +1069,16 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>6882.19</v>
+        <v>6355.98</v>
       </c>
       <c r="F13" t="n">
-        <v>20560.95</v>
+        <v>22854.9</v>
       </c>
       <c r="G13" t="n">
-        <v>540</v>
+        <v>343</v>
       </c>
       <c r="H13" t="n">
-        <v>5555.62</v>
+        <v>4727.54</v>
       </c>
     </row>
     <row r="14">
@@ -1095,16 +1095,16 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>7031.49</v>
+        <v>5931.64</v>
       </c>
       <c r="F14" t="n">
-        <v>21382.45</v>
+        <v>20883.19</v>
       </c>
       <c r="G14" t="n">
-        <v>540</v>
+        <v>340</v>
       </c>
       <c r="H14" t="n">
-        <v>5126.16</v>
+        <v>4191.48</v>
       </c>
     </row>
     <row r="15">
@@ -1121,16 +1121,16 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>7197.44</v>
+        <v>6113.66</v>
       </c>
       <c r="F15" t="n">
-        <v>22237.19</v>
+        <v>21743.29</v>
       </c>
       <c r="G15" t="n">
-        <v>540</v>
+        <v>343</v>
       </c>
       <c r="H15" t="n">
-        <v>5161.39</v>
+        <v>4264.66</v>
       </c>
     </row>
     <row r="16">
@@ -1147,16 +1147,16 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>7288.25</v>
+        <v>6551.43</v>
       </c>
       <c r="F16" t="n">
-        <v>22366.23</v>
+        <v>23707.13</v>
       </c>
       <c r="G16" t="n">
-        <v>547</v>
+        <v>346</v>
       </c>
       <c r="H16" t="n">
-        <v>5871.19</v>
+        <v>4830.45</v>
       </c>
     </row>
     <row r="17">
@@ -1173,16 +1173,16 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>6866.98</v>
+        <v>5669.77</v>
       </c>
       <c r="F17" t="n">
-        <v>20434.91</v>
+        <v>19523.85</v>
       </c>
       <c r="G17" t="n">
-        <v>546</v>
+        <v>343</v>
       </c>
       <c r="H17" t="n">
-        <v>5438.03</v>
+        <v>4241.15</v>
       </c>
     </row>
     <row r="18">
@@ -1199,16 +1199,16 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>7358.32</v>
+        <v>6314.17</v>
       </c>
       <c r="F18" t="n">
-        <v>22941.61</v>
+        <v>22645.83</v>
       </c>
       <c r="G18" t="n">
-        <v>540</v>
+        <v>343</v>
       </c>
       <c r="H18" t="n">
-        <v>5714.16</v>
+        <v>4430.85</v>
       </c>
     </row>
     <row r="19">
@@ -1225,16 +1225,16 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>7263.44</v>
+        <v>6034.35</v>
       </c>
       <c r="F19" t="n">
-        <v>22542.19</v>
+        <v>21396.75</v>
       </c>
       <c r="G19" t="n">
-        <v>540</v>
+        <v>340</v>
       </c>
       <c r="H19" t="n">
-        <v>5388.7</v>
+        <v>4316.24</v>
       </c>
     </row>
     <row r="20">
@@ -1251,16 +1251,16 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>7427.62</v>
+        <v>6284.43</v>
       </c>
       <c r="F20" t="n">
-        <v>23263.11</v>
+        <v>22622.16</v>
       </c>
       <c r="G20" t="n">
-        <v>543</v>
+        <v>340</v>
       </c>
       <c r="H20" t="n">
-        <v>5236.01</v>
+        <v>4153.63</v>
       </c>
     </row>
     <row r="21">
@@ -1277,16 +1277,16 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>7234.92</v>
+        <v>5987.12</v>
       </c>
       <c r="F21" t="n">
-        <v>22349.59</v>
+        <v>21110.61</v>
       </c>
       <c r="G21" t="n">
-        <v>540</v>
+        <v>340</v>
       </c>
       <c r="H21" t="n">
-        <v>5735.93</v>
+        <v>4531.52</v>
       </c>
     </row>
     <row r="22">
@@ -1303,16 +1303,16 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>7571.98</v>
+        <v>6202.49</v>
       </c>
       <c r="F22" t="n">
-        <v>23784.92</v>
+        <v>22087.45</v>
       </c>
       <c r="G22" t="n">
-        <v>549</v>
+        <v>343</v>
       </c>
       <c r="H22" t="n">
-        <v>5768.53</v>
+        <v>4411.85</v>
       </c>
     </row>
     <row r="23">
@@ -1329,16 +1329,16 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>7104.06</v>
+        <v>6283.23</v>
       </c>
       <c r="F23" t="n">
-        <v>21620.29</v>
+        <v>22591.16</v>
       </c>
       <c r="G23" t="n">
-        <v>543</v>
+        <v>340</v>
       </c>
       <c r="H23" t="n">
-        <v>5758.52</v>
+        <v>4702.18</v>
       </c>
     </row>
     <row r="24">
@@ -1355,16 +1355,16 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>7685.51</v>
+        <v>6751.73</v>
       </c>
       <c r="F24" t="n">
-        <v>24602.57</v>
+        <v>24833.64</v>
       </c>
       <c r="G24" t="n">
-        <v>540</v>
+        <v>344</v>
       </c>
       <c r="H24" t="n">
-        <v>4645.55</v>
+        <v>3746.63</v>
       </c>
     </row>
     <row r="25">
@@ -1381,16 +1381,16 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>7391.93</v>
+        <v>6150.67</v>
       </c>
       <c r="F25" t="n">
-        <v>23134.66</v>
+        <v>21853.33</v>
       </c>
       <c r="G25" t="n">
-        <v>540</v>
+        <v>343</v>
       </c>
       <c r="H25" t="n">
-        <v>5130.96</v>
+        <v>3836.92</v>
       </c>
     </row>
     <row r="26">
@@ -1407,16 +1407,16 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>6663.2</v>
+        <v>5599.69</v>
       </c>
       <c r="F26" t="n">
-        <v>19566</v>
+        <v>19248.43</v>
       </c>
       <c r="G26" t="n">
-        <v>540</v>
+        <v>340</v>
       </c>
       <c r="H26" t="n">
-        <v>5411.15</v>
+        <v>4009.05</v>
       </c>
     </row>
     <row r="27">
@@ -1433,16 +1433,16 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>6814.75</v>
+        <v>5797.78</v>
       </c>
       <c r="F27" t="n">
-        <v>20248.75</v>
+        <v>20163.89</v>
       </c>
       <c r="G27" t="n">
-        <v>543</v>
+        <v>343</v>
       </c>
       <c r="H27" t="n">
-        <v>4913.1</v>
+        <v>4074.74</v>
       </c>
     </row>
     <row r="28">
@@ -1459,16 +1459,16 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>7415.44</v>
+        <v>6468.02</v>
       </c>
       <c r="F28" t="n">
-        <v>23202.2</v>
+        <v>23465.09</v>
       </c>
       <c r="G28" t="n">
-        <v>540</v>
+        <v>340</v>
       </c>
       <c r="H28" t="n">
-        <v>4982.98</v>
+        <v>4148.29</v>
       </c>
     </row>
     <row r="29">
@@ -1485,16 +1485,16 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>7648.13</v>
+        <v>7032.59</v>
       </c>
       <c r="F29" t="n">
-        <v>24290.67</v>
+        <v>26212.97</v>
       </c>
       <c r="G29" t="n">
-        <v>543</v>
+        <v>343</v>
       </c>
       <c r="H29" t="n">
-        <v>5418.57</v>
+        <v>4624.55</v>
       </c>
     </row>
     <row r="30">
@@ -1511,16 +1511,16 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>6877.72</v>
+        <v>5872.73</v>
       </c>
       <c r="F30" t="n">
-        <v>20563.62</v>
+        <v>20463.63</v>
       </c>
       <c r="G30" t="n">
-        <v>543</v>
+        <v>346</v>
       </c>
       <c r="H30" t="n">
-        <v>5613.92</v>
+        <v>4472.94</v>
       </c>
     </row>
     <row r="31">
@@ -1537,16 +1537,16 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>6709.53</v>
+        <v>5945.8</v>
       </c>
       <c r="F31" t="n">
-        <v>19747.67</v>
+        <v>20779.02</v>
       </c>
       <c r="G31" t="n">
-        <v>540</v>
+        <v>346</v>
       </c>
       <c r="H31" t="n">
-        <v>5469.19</v>
+        <v>4497.61</v>
       </c>
     </row>
   </sheetData>
@@ -1619,16 +1619,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>15497.43</v>
+        <v>12387.6</v>
       </c>
       <c r="F2" t="n">
-        <v>42537.17</v>
+        <v>36463</v>
       </c>
       <c r="G2" t="n">
-        <v>1383</v>
+        <v>1004</v>
       </c>
       <c r="H2" t="n">
-        <v>12248.57</v>
+        <v>9479.32</v>
       </c>
     </row>
     <row r="3">
@@ -1645,16 +1645,16 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>14690.12</v>
+        <v>11140.17</v>
       </c>
       <c r="F3" t="n">
-        <v>38550.6</v>
+        <v>30450.83</v>
       </c>
       <c r="G3" t="n">
-        <v>1386</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>13532.72</v>
+        <v>9842.379999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1671,16 +1671,16 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>15302.18</v>
+        <v>11922.84</v>
       </c>
       <c r="F4" t="n">
-        <v>41685.91</v>
+        <v>34289.22</v>
       </c>
       <c r="G4" t="n">
-        <v>1380</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>13266.87</v>
+        <v>9707.99</v>
       </c>
     </row>
     <row r="5">
@@ -1697,16 +1697,16 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>15184.32</v>
+        <v>11313.03</v>
       </c>
       <c r="F5" t="n">
-        <v>41121.59</v>
+        <v>31265.16</v>
       </c>
       <c r="G5" t="n">
-        <v>1380</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>13134.87</v>
+        <v>9612.58</v>
       </c>
     </row>
     <row r="6">
@@ -1723,16 +1723,16 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>14946.7</v>
+        <v>11698.38</v>
       </c>
       <c r="F6" t="n">
-        <v>39933.48</v>
+        <v>33091.92</v>
       </c>
       <c r="G6" t="n">
-        <v>1382</v>
+        <v>1006</v>
       </c>
       <c r="H6" t="n">
-        <v>11713.23</v>
+        <v>8220.639999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1749,16 +1749,16 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>14668.62</v>
+        <v>11790.59</v>
       </c>
       <c r="F7" t="n">
-        <v>39793.1</v>
+        <v>33502.96</v>
       </c>
       <c r="G7" t="n">
-        <v>1330</v>
+        <v>1006</v>
       </c>
       <c r="H7" t="n">
-        <v>12258.03</v>
+        <v>9426.67</v>
       </c>
     </row>
     <row r="8">
@@ -1775,16 +1775,16 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>15250.59</v>
+        <v>12180.1</v>
       </c>
       <c r="F8" t="n">
-        <v>41327.93</v>
+        <v>35300.49</v>
       </c>
       <c r="G8" t="n">
-        <v>1383</v>
+        <v>1010</v>
       </c>
       <c r="H8" t="n">
-        <v>13087.76</v>
+        <v>10010.94</v>
       </c>
     </row>
     <row r="9">
@@ -1801,16 +1801,16 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>15073.24</v>
+        <v>11420.34</v>
       </c>
       <c r="F9" t="n">
-        <v>40541.2</v>
+        <v>31751.72</v>
       </c>
       <c r="G9" t="n">
-        <v>1383</v>
+        <v>1004</v>
       </c>
       <c r="H9" t="n">
-        <v>13027.26</v>
+        <v>9438.65</v>
       </c>
     </row>
     <row r="10">
@@ -1827,16 +1827,16 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>15254.03</v>
+        <v>11654.9</v>
       </c>
       <c r="F10" t="n">
-        <v>41945.16</v>
+        <v>33524.49</v>
       </c>
       <c r="G10" t="n">
-        <v>1360</v>
+        <v>977</v>
       </c>
       <c r="H10" t="n">
-        <v>13536.68</v>
+        <v>9958.99</v>
       </c>
     </row>
     <row r="11">
@@ -1853,16 +1853,16 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>14645.26</v>
+        <v>10891.66</v>
       </c>
       <c r="F11" t="n">
-        <v>38451.29</v>
+        <v>29183.29</v>
       </c>
       <c r="G11" t="n">
-        <v>1380</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>13346.26</v>
+        <v>9475.16</v>
       </c>
     </row>
     <row r="12">
@@ -1879,16 +1879,16 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>15341.84</v>
+        <v>11522.39</v>
       </c>
       <c r="F12" t="n">
-        <v>41734.2</v>
+        <v>32161.97</v>
       </c>
       <c r="G12" t="n">
-        <v>1387</v>
+        <v>1006</v>
       </c>
       <c r="H12" t="n">
-        <v>12816.94</v>
+        <v>9574.32</v>
       </c>
     </row>
     <row r="13">
@@ -1905,16 +1905,16 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>15424.89</v>
+        <v>11835.15</v>
       </c>
       <c r="F13" t="n">
-        <v>42124.45</v>
+        <v>33825.74</v>
       </c>
       <c r="G13" t="n">
-        <v>1386</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>12830.83</v>
+        <v>9046.889999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1931,16 +1931,16 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>14716.6</v>
+        <v>11343.61</v>
       </c>
       <c r="F14" t="n">
-        <v>38733.01</v>
+        <v>31218.05</v>
       </c>
       <c r="G14" t="n">
-        <v>1383</v>
+        <v>1009</v>
       </c>
       <c r="H14" t="n">
-        <v>12727.4</v>
+        <v>8757.68</v>
       </c>
     </row>
     <row r="15">
@@ -1957,16 +1957,16 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>15004.98</v>
+        <v>11538.57</v>
       </c>
       <c r="F15" t="n">
-        <v>40199.91</v>
+        <v>32442.87</v>
       </c>
       <c r="G15" t="n">
-        <v>1383</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>12487.21</v>
+        <v>8411.27</v>
       </c>
     </row>
     <row r="16">
@@ -1983,16 +1983,16 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>15319.94</v>
+        <v>11807.14</v>
       </c>
       <c r="F16" t="n">
-        <v>41474.69</v>
+        <v>33485.72</v>
       </c>
       <c r="G16" t="n">
-        <v>1389</v>
+        <v>1006</v>
       </c>
       <c r="H16" t="n">
-        <v>13517.14</v>
+        <v>9432.17</v>
       </c>
     </row>
     <row r="17">
@@ -2009,16 +2009,16 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>15036.3</v>
+        <v>11448.13</v>
       </c>
       <c r="F17" t="n">
-        <v>40431.48</v>
+        <v>31815.65</v>
       </c>
       <c r="G17" t="n">
-        <v>1380</v>
+        <v>1007</v>
       </c>
       <c r="H17" t="n">
-        <v>11363.82</v>
+        <v>9017.66</v>
       </c>
     </row>
     <row r="18">
@@ -2035,16 +2035,16 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>15355.69</v>
+        <v>11961.46</v>
       </c>
       <c r="F18" t="n">
-        <v>41853.46</v>
+        <v>34382.29</v>
       </c>
       <c r="G18" t="n">
-        <v>1383</v>
+        <v>1003</v>
       </c>
       <c r="H18" t="n">
-        <v>12038.47</v>
+        <v>9512.540000000001</v>
       </c>
     </row>
     <row r="19">
@@ -2061,16 +2061,16 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>14758.24</v>
+        <v>11592.85</v>
       </c>
       <c r="F19" t="n">
-        <v>39016.22</v>
+        <v>32689.27</v>
       </c>
       <c r="G19" t="n">
-        <v>1380</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>13279.43</v>
+        <v>9159.65</v>
       </c>
     </row>
     <row r="20">
@@ -2087,16 +2087,16 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>15263.71</v>
+        <v>11680.41</v>
       </c>
       <c r="F20" t="n">
-        <v>41518.56</v>
+        <v>33102.04</v>
       </c>
       <c r="G20" t="n">
-        <v>1380</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>13041.71</v>
+        <v>9685.110000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2113,16 +2113,16 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>14643.38</v>
+        <v>11466.92</v>
       </c>
       <c r="F21" t="n">
-        <v>38391.91</v>
+        <v>32009.58</v>
       </c>
       <c r="G21" t="n">
-        <v>1380</v>
+        <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>12200.81</v>
+        <v>9373.389999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2139,16 +2139,16 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>15037.65</v>
+        <v>11620.94</v>
       </c>
       <c r="F22" t="n">
-        <v>40338.27</v>
+        <v>32754.71</v>
       </c>
       <c r="G22" t="n">
-        <v>1380</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>12617.49</v>
+        <v>8966.799999999999</v>
       </c>
     </row>
     <row r="23">
@@ -2165,16 +2165,16 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>15142.76</v>
+        <v>11504.79</v>
       </c>
       <c r="F23" t="n">
-        <v>40813.8</v>
+        <v>32123.93</v>
       </c>
       <c r="G23" t="n">
-        <v>1383</v>
+        <v>1003</v>
       </c>
       <c r="H23" t="n">
-        <v>13187.32</v>
+        <v>9311.440000000001</v>
       </c>
     </row>
     <row r="24">
@@ -2191,16 +2191,16 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>15213.95</v>
+        <v>12430.36</v>
       </c>
       <c r="F24" t="n">
-        <v>41169.77</v>
+        <v>36751.79</v>
       </c>
       <c r="G24" t="n">
-        <v>1383</v>
+        <v>1003</v>
       </c>
       <c r="H24" t="n">
-        <v>12240.14</v>
+        <v>8932.34</v>
       </c>
     </row>
     <row r="25">
@@ -2217,16 +2217,16 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>15018.53</v>
+        <v>12165.8</v>
       </c>
       <c r="F25" t="n">
-        <v>40267.64</v>
+        <v>35503.99</v>
       </c>
       <c r="G25" t="n">
-        <v>1380</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>12921.39</v>
+        <v>8883.049999999999</v>
       </c>
     </row>
     <row r="26">
@@ -2243,16 +2243,16 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>14803.72</v>
+        <v>11702.73</v>
       </c>
       <c r="F26" t="n">
-        <v>39118.59</v>
+        <v>33113.66</v>
       </c>
       <c r="G26" t="n">
-        <v>1386</v>
+        <v>1006</v>
       </c>
       <c r="H26" t="n">
-        <v>13043.43</v>
+        <v>9445.16</v>
       </c>
     </row>
     <row r="27">
@@ -2269,16 +2269,16 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>14985.56</v>
+        <v>11760.97</v>
       </c>
       <c r="F27" t="n">
-        <v>40027.8</v>
+        <v>33479.85</v>
       </c>
       <c r="G27" t="n">
-        <v>1386</v>
+        <v>1003</v>
       </c>
       <c r="H27" t="n">
-        <v>12620.81</v>
+        <v>8748.6</v>
       </c>
     </row>
     <row r="28">
@@ -2295,16 +2295,16 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>15221.87</v>
+        <v>11491.63</v>
       </c>
       <c r="F28" t="n">
-        <v>41159.33</v>
+        <v>31933.13</v>
       </c>
       <c r="G28" t="n">
-        <v>1383</v>
+        <v>1006</v>
       </c>
       <c r="H28" t="n">
-        <v>13609.65</v>
+        <v>9967.290000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2321,16 +2321,16 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>16074.79</v>
+        <v>12345.34</v>
       </c>
       <c r="F29" t="n">
-        <v>45423.96</v>
+        <v>36276.72</v>
       </c>
       <c r="G29" t="n">
-        <v>1383</v>
+        <v>1003</v>
       </c>
       <c r="H29" t="n">
-        <v>12811.22</v>
+        <v>9294.23</v>
       </c>
     </row>
     <row r="30">
@@ -2347,16 +2347,16 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>14903.07</v>
+        <v>11205.12</v>
       </c>
       <c r="F30" t="n">
-        <v>39690.37</v>
+        <v>30775.58</v>
       </c>
       <c r="G30" t="n">
-        <v>1383</v>
+        <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>12572.7</v>
+        <v>9260.889999999999</v>
       </c>
     </row>
     <row r="31">
@@ -2373,16 +2373,16 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>14883.81</v>
+        <v>11213.12</v>
       </c>
       <c r="F31" t="n">
-        <v>39544.04</v>
+        <v>30765.6</v>
       </c>
       <c r="G31" t="n">
-        <v>1383</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>13361.19</v>
+        <v>9541.68</v>
       </c>
     </row>
   </sheetData>

--- a/projects/cumcm2026b/artifacts/results/resultB.xlsx
+++ b/projects/cumcm2026b/artifacts/results/resultB.xlsx
@@ -1619,16 +1619,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>12387.6</v>
+        <v>9905.66</v>
       </c>
       <c r="F2" t="n">
-        <v>36463</v>
+        <v>34578.32</v>
       </c>
       <c r="G2" t="n">
-        <v>1004</v>
+        <v>583</v>
       </c>
       <c r="H2" t="n">
-        <v>9479.32</v>
+        <v>7271.67</v>
       </c>
     </row>
     <row r="3">
@@ -1645,16 +1645,16 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>11140.17</v>
+        <v>9020.85</v>
       </c>
       <c r="F3" t="n">
-        <v>30450.83</v>
+        <v>30029.26</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>593</v>
       </c>
       <c r="H3" t="n">
-        <v>9842.379999999999</v>
+        <v>7546.25</v>
       </c>
     </row>
     <row r="4">
@@ -1671,16 +1671,16 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>11922.84</v>
+        <v>9309.540000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>34289.22</v>
+        <v>31647.71</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>583</v>
       </c>
       <c r="H4" t="n">
-        <v>9707.99</v>
+        <v>7097.34</v>
       </c>
     </row>
     <row r="5">
@@ -1697,16 +1697,16 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>11313.03</v>
+        <v>8835.530000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>31265.16</v>
+        <v>29377.66</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="H5" t="n">
-        <v>9612.58</v>
+        <v>7106.01</v>
       </c>
     </row>
     <row r="6">
@@ -1723,16 +1723,16 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>11698.38</v>
+        <v>8973.719999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>33091.92</v>
+        <v>30118.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1006</v>
+        <v>580</v>
       </c>
       <c r="H6" t="n">
-        <v>8220.639999999999</v>
+        <v>5864.16</v>
       </c>
     </row>
     <row r="7">
@@ -1749,16 +1749,16 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>11790.59</v>
+        <v>9082.25</v>
       </c>
       <c r="F7" t="n">
-        <v>33502.96</v>
+        <v>30536.24</v>
       </c>
       <c r="G7" t="n">
-        <v>1006</v>
+        <v>583</v>
       </c>
       <c r="H7" t="n">
-        <v>9426.67</v>
+        <v>6975.61</v>
       </c>
     </row>
     <row r="8">
@@ -1775,16 +1775,16 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>12180.1</v>
+        <v>9276.25</v>
       </c>
       <c r="F8" t="n">
-        <v>35300.49</v>
+        <v>31356.25</v>
       </c>
       <c r="G8" t="n">
-        <v>1010</v>
+        <v>587</v>
       </c>
       <c r="H8" t="n">
-        <v>10010.94</v>
+        <v>7358.62</v>
       </c>
     </row>
     <row r="9">
@@ -1801,16 +1801,16 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>11420.34</v>
+        <v>8711.41</v>
       </c>
       <c r="F9" t="n">
-        <v>31751.72</v>
+        <v>28657.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1004</v>
+        <v>586</v>
       </c>
       <c r="H9" t="n">
-        <v>9438.65</v>
+        <v>7200.18</v>
       </c>
     </row>
     <row r="10">
@@ -1827,16 +1827,16 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>11654.9</v>
+        <v>9341.65</v>
       </c>
       <c r="F10" t="n">
-        <v>33524.49</v>
+        <v>31733.24</v>
       </c>
       <c r="G10" t="n">
-        <v>977</v>
+        <v>586</v>
       </c>
       <c r="H10" t="n">
-        <v>9958.99</v>
+        <v>7842.59</v>
       </c>
     </row>
     <row r="11">
@@ -1853,16 +1853,16 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>10891.66</v>
+        <v>8687.870000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>29183.29</v>
+        <v>28514.36</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>586</v>
       </c>
       <c r="H11" t="n">
-        <v>9475.16</v>
+        <v>6931.57</v>
       </c>
     </row>
     <row r="12">
@@ -1879,16 +1879,16 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>11522.39</v>
+        <v>9232.99</v>
       </c>
       <c r="F12" t="n">
-        <v>32161.97</v>
+        <v>31364.96</v>
       </c>
       <c r="G12" t="n">
-        <v>1006</v>
+        <v>580</v>
       </c>
       <c r="H12" t="n">
-        <v>9574.32</v>
+        <v>7154.18</v>
       </c>
     </row>
     <row r="13">
@@ -1905,16 +1905,16 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>11835.15</v>
+        <v>9240.67</v>
       </c>
       <c r="F13" t="n">
-        <v>33825.74</v>
+        <v>31278.33</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>583</v>
       </c>
       <c r="H13" t="n">
-        <v>9046.889999999999</v>
+        <v>6444.45</v>
       </c>
     </row>
     <row r="14">
@@ -1931,16 +1931,16 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>11343.61</v>
+        <v>9916.190000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>31218.05</v>
+        <v>33405.94</v>
       </c>
       <c r="G14" t="n">
-        <v>1009</v>
+        <v>636</v>
       </c>
       <c r="H14" t="n">
-        <v>8757.68</v>
+        <v>6105.86</v>
       </c>
     </row>
     <row r="15">
@@ -1957,16 +1957,16 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>11538.57</v>
+        <v>8807.450000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>32442.87</v>
+        <v>29287.25</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="H15" t="n">
-        <v>8411.27</v>
+        <v>5707.53</v>
       </c>
     </row>
     <row r="16">
@@ -1983,16 +1983,16 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>11807.14</v>
+        <v>9015.07</v>
       </c>
       <c r="F16" t="n">
-        <v>33485.72</v>
+        <v>30100.33</v>
       </c>
       <c r="G16" t="n">
-        <v>1006</v>
+        <v>583</v>
       </c>
       <c r="H16" t="n">
-        <v>9432.17</v>
+        <v>6693.27</v>
       </c>
     </row>
     <row r="17">
@@ -2009,16 +2009,16 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>11448.13</v>
+        <v>9114.940000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>31815.65</v>
+        <v>30749.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1007</v>
+        <v>583</v>
       </c>
       <c r="H17" t="n">
-        <v>9017.66</v>
+        <v>6480.77</v>
       </c>
     </row>
     <row r="18">
@@ -2035,16 +2035,16 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>11961.46</v>
+        <v>9344.559999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>34382.29</v>
+        <v>31872.8</v>
       </c>
       <c r="G18" t="n">
-        <v>1003</v>
+        <v>580</v>
       </c>
       <c r="H18" t="n">
-        <v>9512.540000000001</v>
+        <v>6911.44</v>
       </c>
     </row>
     <row r="19">
@@ -2061,16 +2061,16 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>11592.85</v>
+        <v>9125.379999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>32689.27</v>
+        <v>30851.92</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="H19" t="n">
-        <v>9159.65</v>
+        <v>6879.4</v>
       </c>
     </row>
     <row r="20">
@@ -2087,16 +2087,16 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>11680.41</v>
+        <v>9252.959999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>33102.04</v>
+        <v>31389.81</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>583</v>
       </c>
       <c r="H20" t="n">
-        <v>9685.110000000001</v>
+        <v>7342.8</v>
       </c>
     </row>
     <row r="21">
@@ -2113,16 +2113,16 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>11466.92</v>
+        <v>9152.01</v>
       </c>
       <c r="F21" t="n">
-        <v>32009.58</v>
+        <v>30860.06</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>583</v>
       </c>
       <c r="H21" t="n">
-        <v>9373.389999999999</v>
+        <v>6766.26</v>
       </c>
     </row>
     <row r="22">
@@ -2139,16 +2139,16 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>11620.94</v>
+        <v>11462.59</v>
       </c>
       <c r="F22" t="n">
-        <v>32754.71</v>
+        <v>40012.95</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>678</v>
       </c>
       <c r="H22" t="n">
-        <v>8966.799999999999</v>
+        <v>6800.67</v>
       </c>
     </row>
     <row r="23">
@@ -2165,16 +2165,16 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>11504.79</v>
+        <v>9209.629999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>32123.93</v>
+        <v>31223.16</v>
       </c>
       <c r="G23" t="n">
-        <v>1003</v>
+        <v>580</v>
       </c>
       <c r="H23" t="n">
-        <v>9311.440000000001</v>
+        <v>6904.77</v>
       </c>
     </row>
     <row r="24">
@@ -2191,16 +2191,16 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>12430.36</v>
+        <v>9525.530000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>36751.79</v>
+        <v>32577.63</v>
       </c>
       <c r="G24" t="n">
-        <v>1003</v>
+        <v>589</v>
       </c>
       <c r="H24" t="n">
-        <v>8932.34</v>
+        <v>6283.02</v>
       </c>
     </row>
     <row r="25">
@@ -2217,16 +2217,16 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>12165.8</v>
+        <v>9583.25</v>
       </c>
       <c r="F25" t="n">
-        <v>35503.99</v>
+        <v>33091.26</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="H25" t="n">
-        <v>8883.049999999999</v>
+        <v>6198.43</v>
       </c>
     </row>
     <row r="26">
@@ -2243,16 +2243,16 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>11702.73</v>
+        <v>8830.75</v>
       </c>
       <c r="F26" t="n">
-        <v>33113.66</v>
+        <v>29403.75</v>
       </c>
       <c r="G26" t="n">
-        <v>1006</v>
+        <v>580</v>
       </c>
       <c r="H26" t="n">
-        <v>9445.16</v>
+        <v>7059.86</v>
       </c>
     </row>
     <row r="27">
@@ -2269,16 +2269,16 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>11760.97</v>
+        <v>17593.66</v>
       </c>
       <c r="F27" t="n">
-        <v>33479.85</v>
+        <v>61418.3</v>
       </c>
       <c r="G27" t="n">
-        <v>1003</v>
+        <v>1052</v>
       </c>
       <c r="H27" t="n">
-        <v>8748.6</v>
+        <v>9610.530000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2295,16 +2295,16 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>11491.63</v>
+        <v>9440.51</v>
       </c>
       <c r="F28" t="n">
-        <v>31933.13</v>
+        <v>32177.56</v>
       </c>
       <c r="G28" t="n">
-        <v>1006</v>
+        <v>586</v>
       </c>
       <c r="H28" t="n">
-        <v>9967.290000000001</v>
+        <v>7548.48</v>
       </c>
     </row>
     <row r="29">
@@ -2321,16 +2321,16 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>12345.34</v>
+        <v>10536.17</v>
       </c>
       <c r="F29" t="n">
-        <v>36276.72</v>
+        <v>37655.86</v>
       </c>
       <c r="G29" t="n">
-        <v>1003</v>
+        <v>586</v>
       </c>
       <c r="H29" t="n">
-        <v>9294.23</v>
+        <v>6959</v>
       </c>
     </row>
     <row r="30">
@@ -2347,16 +2347,16 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>11205.12</v>
+        <v>8855.51</v>
       </c>
       <c r="F30" t="n">
-        <v>30775.58</v>
+        <v>29377.53</v>
       </c>
       <c r="G30" t="n">
-        <v>1000</v>
+        <v>586</v>
       </c>
       <c r="H30" t="n">
-        <v>9260.889999999999</v>
+        <v>6642.8</v>
       </c>
     </row>
     <row r="31">
@@ -2373,16 +2373,16 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>11213.12</v>
+        <v>9115.41</v>
       </c>
       <c r="F31" t="n">
-        <v>30765.6</v>
+        <v>30702.05</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>583</v>
       </c>
       <c r="H31" t="n">
-        <v>9541.68</v>
+        <v>7012.87</v>
       </c>
     </row>
   </sheetData>
